--- a/Data/Character.xlsx
+++ b/Data/Character.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoldenMansion\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2FF3DC-58F9-497E-AC24-EF737782DEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809B13C2-40FE-4D63-8570-E1B8B2BF6862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="224">
   <si>
     <t>名字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -280,9 +280,6 @@
     <t>GuestPortrait/meiti</t>
   </si>
   <si>
-    <t>小编哥</t>
-  </si>
-  <si>
     <t>导游哥</t>
   </si>
   <si>
@@ -422,303 +419,361 @@
     <t>INTJ</t>
   </si>
   <si>
+    <t>ENTP</t>
+  </si>
+  <si>
+    <t>INFJ</t>
+  </si>
+  <si>
+    <t>INFP</t>
+  </si>
+  <si>
+    <t>ENFJ</t>
+  </si>
+  <si>
+    <t>ENFP</t>
+  </si>
+  <si>
+    <t>ISTJ</t>
+  </si>
+  <si>
+    <t>ISFJ</t>
+  </si>
+  <si>
+    <t>ESTJ</t>
+  </si>
+  <si>
+    <t>ESFJ</t>
+  </si>
+  <si>
+    <t>ISTP</t>
+  </si>
+  <si>
+    <t>ISFP</t>
+  </si>
+  <si>
+    <t>ESTP</t>
+  </si>
+  <si>
+    <t>ESFP</t>
+  </si>
+  <si>
+    <t>内向</t>
+  </si>
+  <si>
+    <t>外向</t>
+  </si>
+  <si>
+    <t>细心</t>
+  </si>
+  <si>
+    <t>抽象</t>
+  </si>
+  <si>
+    <t>感性</t>
+  </si>
+  <si>
+    <t>理性</t>
+  </si>
+  <si>
+    <t>无法被消除</t>
+  </si>
+  <si>
+    <t>循规蹈矩</t>
+  </si>
+  <si>
+    <t>每回合结束后，租金+1</t>
+  </si>
+  <si>
+    <t>随性</t>
+  </si>
+  <si>
+    <t>icon路径</t>
+  </si>
+  <si>
+    <t>icon路径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能等级条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Persona/I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Persona/E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Persona/J</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Persona/P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Persona/T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Persona/F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Persona/S</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Persona/N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每天，生成一个任意职业的实习生</t>
+  </si>
+  <si>
+    <t>每有一个房客被卖出后，所有租客房租+1</t>
+  </si>
+  <si>
+    <t>每回合结束后，所有租客房租+1</t>
+  </si>
+  <si>
+    <t>持续生效：买入租客的价格降低50%</t>
+  </si>
+  <si>
+    <t>交租时，每有一个外向型，房租+1</t>
+  </si>
+  <si>
+    <t>交租后，每有5元余额，额外获得1元</t>
+  </si>
+  <si>
+    <t>持续生效：使所有实习生房租+1</t>
+  </si>
+  <si>
+    <t>持续生效：交租时，空房间也可提供+5租金</t>
+  </si>
+  <si>
+    <t>若没有邻居，租金随机增加1~10</t>
+  </si>
+  <si>
+    <t>获得邻居最高的房租</t>
+  </si>
+  <si>
+    <t>若没有邻居，则生成8个随机租客，然后离开</t>
+  </si>
+  <si>
+    <t>持续生效：交租前，周围每有一个空房间，租金+10</t>
+  </si>
+  <si>
+    <t>若基础租金比所有邻居都高，则让邻居租金等于他的租金</t>
+  </si>
+  <si>
+    <t>若所有邻居都是ESFP，这局游戏胜利</t>
+  </si>
+  <si>
+    <t>GuestPortrait/gaozhongsheng</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/quanshangge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/jinrongshixige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/youxishixige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/cehuage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/ziyouzhiye</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/peixunge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/jiaoyushixige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/kefuge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/dianshangshixige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/tiyuge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/tiyushixige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/fangdichanshixige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/yishuge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/yishushixige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/canyinge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/canyinshixige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/meitige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/lvyouge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/lvyoushixige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/zhubaoge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/zhubaoshixige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/yiliaoge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/yiliaoshixige</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/shiyege</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>INTP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ENTJ</t>
-  </si>
-  <si>
-    <t>ENTP</t>
-  </si>
-  <si>
-    <t>INFJ</t>
-  </si>
-  <si>
-    <t>INFP</t>
-  </si>
-  <si>
-    <t>ENFJ</t>
-  </si>
-  <si>
-    <t>ENFP</t>
-  </si>
-  <si>
-    <t>ISTJ</t>
-  </si>
-  <si>
-    <t>ISFJ</t>
-  </si>
-  <si>
-    <t>ESTJ</t>
-  </si>
-  <si>
-    <t>ESFJ</t>
-  </si>
-  <si>
-    <t>ISTP</t>
-  </si>
-  <si>
-    <t>ISFP</t>
-  </si>
-  <si>
-    <t>ESTP</t>
-  </si>
-  <si>
-    <t>ESFP</t>
-  </si>
-  <si>
-    <t>内向</t>
-  </si>
-  <si>
-    <t>消除周围的人</t>
-  </si>
-  <si>
-    <t>外向</t>
-  </si>
-  <si>
-    <t>被卖出时价格翻倍</t>
-  </si>
-  <si>
-    <t>细心</t>
-  </si>
-  <si>
-    <t>获得一项其他个性</t>
-  </si>
-  <si>
-    <t>抽象</t>
-  </si>
-  <si>
-    <t>50%的概率忘记交租，50%的概率上交双倍房租</t>
-  </si>
-  <si>
-    <t>感性</t>
-  </si>
-  <si>
-    <t>每有房客被卖出，有概率离开</t>
-  </si>
-  <si>
-    <t>理性</t>
-  </si>
-  <si>
-    <t>无法被消除</t>
-  </si>
-  <si>
-    <t>循规蹈矩</t>
-  </si>
-  <si>
-    <t>每回合结束后，租金+1</t>
-  </si>
-  <si>
-    <t>随性</t>
-  </si>
-  <si>
-    <t>每X天随机变成其他职业</t>
-  </si>
-  <si>
-    <t>icon路径</t>
-  </si>
-  <si>
-    <t>icon路径</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能等级条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skillLevel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persona/I</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persona/E</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persona/J</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persona/P</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persona/T</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persona/F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persona/S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Persona/N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每天，生成一个任意职业的实习生</t>
-  </si>
-  <si>
-    <t>每有一个房客被卖出后，所有租客房租+1</t>
-  </si>
-  <si>
-    <t>获得后触发：选择一个租客，使其房租翻倍</t>
-  </si>
-  <si>
-    <t>每回合结束后，所有租客房租+1</t>
-  </si>
-  <si>
-    <t>持续生效：买入租客的价格降低50%</t>
-  </si>
-  <si>
-    <t>获得后触发：使所有租客变为外向型</t>
-  </si>
-  <si>
-    <t>交租时，每有一个外向型，房租+1</t>
-  </si>
-  <si>
-    <t>交租后，每有5元余额，额外获得1元</t>
-  </si>
-  <si>
-    <t>持续生效：使所有实习生房租+1</t>
-  </si>
-  <si>
-    <t>持续生效：交租时，空房间也可提供+5租金</t>
-  </si>
-  <si>
-    <t>若没有邻居，租金随机增加1~10</t>
-  </si>
-  <si>
-    <t>获得邻居最高的房租</t>
-  </si>
-  <si>
-    <t>若没有邻居，则生成8个随机租客，然后离开</t>
-  </si>
-  <si>
-    <t>持续生效：交租前，周围每有一个空房间，租金+10</t>
-  </si>
-  <si>
-    <t>若基础租金比所有邻居都高，则让邻居租金等于他的租金</t>
-  </si>
-  <si>
-    <t>若所有邻居都是ESFP，这局游戏胜利</t>
-  </si>
-  <si>
-    <t>GuestPortrait/gaozhongsheng</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/quanshangge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/jinrongshixige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/youxishixige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/cehuage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/ziyouzhiye</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/peixunge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/jiaoyushixige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/kefuge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/dianshangshixige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/tiyuge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/tiyushixige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/fangdichanshixige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/yishuge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/yishushixige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/canyinge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/canyinshixige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/meitige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/meitishixige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/lvyouge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/lvyoushixige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/zhubaoge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/zhubaoshixige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/yiliaoge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/yiliaoshixige</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GuestPortrait/shiyege</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Persona/INTJ</t>
+  </si>
+  <si>
+    <t>Persona/INTP</t>
+  </si>
+  <si>
+    <t>Persona/ENTJ</t>
+  </si>
+  <si>
+    <t>Persona/ENTP</t>
+  </si>
+  <si>
+    <t>Persona/INFJ</t>
+  </si>
+  <si>
+    <t>Persona/INFP</t>
+  </si>
+  <si>
+    <t>Persona/ENFJ</t>
+  </si>
+  <si>
+    <t>Persona/ENFP</t>
+  </si>
+  <si>
+    <t>Persona/ISTJ</t>
+  </si>
+  <si>
+    <t>Persona/ISFJ</t>
+  </si>
+  <si>
+    <t>Persona/ESTJ</t>
+  </si>
+  <si>
+    <t>Persona/ESFJ</t>
+  </si>
+  <si>
+    <t>Persona/ISTP</t>
+  </si>
+  <si>
+    <t>Persona/ISFP</t>
+  </si>
+  <si>
+    <t>Persona/ESTP</t>
+  </si>
+  <si>
+    <t>Persona/ESFP</t>
+  </si>
+  <si>
+    <t>入住后，消除自身周围的人</t>
+  </si>
+  <si>
+    <t>被卖出时，自身价格翻倍</t>
+  </si>
+  <si>
+    <t>若有X个邻居，则租金翻倍（X每天随机）</t>
+  </si>
+  <si>
+    <t>交租时，50%的概率忘记交租，50%的概率上交双倍房租</t>
+  </si>
+  <si>
+    <t>每有房客被卖出时，有概率离开</t>
+  </si>
+  <si>
+    <t>增加一次重掷机会</t>
+  </si>
+  <si>
+    <t>移除房租比他低的邻居</t>
+  </si>
+  <si>
+    <t>使其邻居的售价永久+1</t>
+  </si>
+  <si>
+    <t>GuestPortrait/daxuesheng</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/yanjiusheng</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuestPortrait/boshisheng</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1048,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:H71"/>
+  <dimension ref="A3:H69"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11.375" customWidth="1"/>
@@ -1152,13 +1207,13 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1178,13 +1233,13 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1204,13 +1259,13 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1230,13 +1285,13 @@
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -1256,13 +1311,13 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -1282,13 +1337,13 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -1308,13 +1363,13 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -1334,13 +1389,13 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -1360,13 +1415,13 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>3</v>
@@ -1386,13 +1441,13 @@
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>3</v>
@@ -1412,13 +1467,13 @@
         <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>3</v>
@@ -1438,13 +1493,13 @@
         <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>3</v>
@@ -1464,13 +1519,13 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <v>3</v>
@@ -1490,13 +1545,13 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H20">
         <v>3</v>
@@ -1516,13 +1571,13 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>4</v>
@@ -1542,13 +1597,13 @@
         <v>2</v>
       </c>
       <c r="E22" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -1568,13 +1623,13 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H23">
         <v>4</v>
@@ -1594,13 +1649,13 @@
         <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H24">
         <v>4</v>
@@ -1620,13 +1675,13 @@
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H25">
         <v>5</v>
@@ -1646,13 +1701,13 @@
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>5</v>
@@ -1672,13 +1727,13 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -1698,13 +1753,13 @@
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H28">
         <v>5</v>
@@ -1724,13 +1779,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -1750,13 +1805,13 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H30">
         <v>6</v>
@@ -1776,13 +1831,13 @@
         <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H31">
         <v>6</v>
@@ -1802,13 +1857,13 @@
         <v>2</v>
       </c>
       <c r="E32" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H32">
         <v>6</v>
@@ -1828,13 +1883,13 @@
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>6</v>
@@ -1854,13 +1909,13 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H34">
         <v>7</v>
@@ -1880,13 +1935,13 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H35">
         <v>7</v>
@@ -1906,13 +1961,13 @@
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>7</v>
@@ -1932,13 +1987,13 @@
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <v>7</v>
@@ -1961,10 +2016,10 @@
         <v>55</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H38">
         <v>8</v>
@@ -1987,10 +2042,10 @@
         <v>55</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H39">
         <v>8</v>
@@ -2013,10 +2068,10 @@
         <v>55</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H40">
         <v>8</v>
@@ -2036,13 +2091,13 @@
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41">
         <v>8</v>
@@ -2062,13 +2117,13 @@
         <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H42">
         <v>9</v>
@@ -2088,13 +2143,13 @@
         <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H43">
         <v>9</v>
@@ -2114,13 +2169,13 @@
         <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H44">
         <v>9</v>
@@ -2140,13 +2195,13 @@
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H45">
         <v>9</v>
@@ -2166,13 +2221,13 @@
         <v>2</v>
       </c>
       <c r="E46" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H46">
         <v>9</v>
@@ -2192,13 +2247,13 @@
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47">
         <v>9</v>
@@ -2218,13 +2273,13 @@
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H48">
         <v>10</v>
@@ -2244,13 +2299,13 @@
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H49">
         <v>10</v>
@@ -2270,13 +2325,13 @@
         <v>2</v>
       </c>
       <c r="E50" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H50">
         <v>10</v>
@@ -2296,13 +2351,13 @@
         <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H51">
         <v>10</v>
@@ -2322,13 +2377,13 @@
         <v>2</v>
       </c>
       <c r="E52" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H52">
         <v>10</v>
@@ -2348,13 +2403,13 @@
         <v>2</v>
       </c>
       <c r="E53" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H53">
         <v>10</v>
@@ -2374,13 +2429,13 @@
         <v>1</v>
       </c>
       <c r="E54" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H54">
         <v>10</v>
@@ -2400,13 +2455,13 @@
         <v>2</v>
       </c>
       <c r="E55" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H55">
         <v>11</v>
@@ -2426,16 +2481,16 @@
         <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H56">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -2443,25 +2498,25 @@
         <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C57">
         <v>1051</v>
       </c>
-      <c r="D57" s="1">
-        <v>1</v>
+      <c r="D57" s="2">
+        <v>2</v>
       </c>
       <c r="E57" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H57">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -2469,22 +2524,22 @@
         <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="C58">
         <v>1052</v>
       </c>
-      <c r="D58" s="1">
-        <v>2</v>
+      <c r="D58" s="2">
+        <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H58">
         <v>12</v>
@@ -2495,7 +2550,7 @@
         <v>53</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C59">
         <v>1053</v>
@@ -2504,16 +2559,16 @@
         <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H59">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -2521,25 +2576,25 @@
         <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C60">
         <v>1054</v>
       </c>
       <c r="D60" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H60">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -2547,7 +2602,7 @@
         <v>55</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C61">
         <v>1055</v>
@@ -2556,13 +2611,13 @@
         <v>2</v>
       </c>
       <c r="E61" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H61">
         <v>13</v>
@@ -2573,22 +2628,22 @@
         <v>56</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C62">
         <v>1056</v>
       </c>
       <c r="D62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H62">
         <v>13</v>
@@ -2608,16 +2663,16 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H63">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -2625,25 +2680,25 @@
         <v>58</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="C64">
         <v>1058</v>
       </c>
       <c r="D64" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H64">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -2651,22 +2706,22 @@
         <v>59</v>
       </c>
       <c r="B65" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="C65">
         <v>1059</v>
       </c>
       <c r="D65" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65">
         <v>14</v>
@@ -2677,7 +2732,7 @@
         <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C66">
         <v>1060</v>
@@ -2686,13 +2741,13 @@
         <v>2</v>
       </c>
       <c r="E66" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H66">
         <v>14</v>
@@ -2703,81 +2758,29 @@
         <v>61</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C67">
         <v>1061</v>
       </c>
       <c r="D67" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>-100</v>
       </c>
       <c r="H67">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <v>62</v>
-      </c>
-      <c r="B68" t="s">
-        <v>57</v>
-      </c>
-      <c r="C68">
-        <v>1062</v>
-      </c>
-      <c r="D68" s="2">
-        <v>2</v>
-      </c>
-      <c r="E68" t="s">
-        <v>204</v>
-      </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
-      <c r="G68">
-        <v>2</v>
-      </c>
-      <c r="H68">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>63</v>
-      </c>
-      <c r="B69" t="s">
-        <v>82</v>
-      </c>
-      <c r="C69">
-        <v>1063</v>
-      </c>
-      <c r="D69" s="2">
-        <v>10</v>
-      </c>
-      <c r="E69" t="s">
-        <v>206</v>
-      </c>
-      <c r="F69">
-        <v>1</v>
-      </c>
-      <c r="G69">
-        <v>2</v>
-      </c>
-      <c r="H69">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="A69" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2798,27 +2801,27 @@
   <sheetData>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
         <v>84</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>85</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>86</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" t="s">
         <v>87</v>
-      </c>
-      <c r="E3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2826,39 +2829,39 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
         <v>91</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>92</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F5" t="s">
         <v>93</v>
-      </c>
-      <c r="E5" t="s">
-        <v>154</v>
-      </c>
-      <c r="F5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
         <v>95</v>
       </c>
-      <c r="B6" t="s">
-        <v>96</v>
-      </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="F6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -2866,7 +2869,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7">
         <v>2001</v>
@@ -2875,7 +2878,7 @@
         <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
@@ -2886,7 +2889,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8">
         <v>2002</v>
@@ -2895,7 +2898,7 @@
         <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
@@ -2906,7 +2909,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9">
         <v>2003</v>
@@ -2915,7 +2918,7 @@
         <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F9" t="s">
         <v>31</v>
@@ -2926,7 +2929,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10">
         <v>2004</v>
@@ -2935,7 +2938,7 @@
         <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F10" t="s">
         <v>38</v>
@@ -2946,7 +2949,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>2005</v>
@@ -2955,7 +2958,7 @@
         <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F11" t="s">
         <v>43</v>
@@ -2966,7 +2969,7 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C12">
         <v>2006</v>
@@ -2975,7 +2978,7 @@
         <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F12" t="s">
         <v>48</v>
@@ -2986,7 +2989,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13">
         <v>2007</v>
@@ -2995,7 +2998,7 @@
         <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F13" t="s">
         <v>51</v>
@@ -3006,7 +3009,7 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C14">
         <v>2008</v>
@@ -3015,7 +3018,7 @@
         <v>57</v>
       </c>
       <c r="E14" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F14" t="s">
         <v>55</v>
@@ -3026,7 +3029,7 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15">
         <v>2009</v>
@@ -3035,7 +3038,7 @@
         <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F15" t="s">
         <v>59</v>
@@ -3046,7 +3049,7 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16">
         <v>2010</v>
@@ -3055,7 +3058,7 @@
         <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F16" t="s">
         <v>65</v>
@@ -3066,7 +3069,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17">
         <v>2011</v>
@@ -3075,7 +3078,7 @@
         <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F17" t="s">
         <v>72</v>
@@ -3086,7 +3089,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18">
         <v>2012</v>
@@ -3095,10 +3098,10 @@
         <v>61</v>
       </c>
       <c r="E18" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -3106,7 +3109,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C19">
         <v>2013</v>
@@ -3115,10 +3118,10 @@
         <v>62</v>
       </c>
       <c r="E19" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -3126,7 +3129,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20">
         <v>2014</v>
@@ -3135,10 +3138,10 @@
         <v>63</v>
       </c>
       <c r="E20" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -3146,7 +3149,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C21">
         <v>2015</v>
@@ -3155,15 +3158,15 @@
         <v>64</v>
       </c>
       <c r="E21" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -3182,30 +3185,30 @@
   <sheetData>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
         <v>84</v>
       </c>
-      <c r="B3" t="s">
-        <v>85</v>
-      </c>
       <c r="C3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" t="s">
         <v>113</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>114</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>115</v>
       </c>
-      <c r="F3" t="s">
-        <v>116</v>
-      </c>
       <c r="G3" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -3213,45 +3216,45 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
         <v>91</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" t="s">
         <v>92</v>
       </c>
-      <c r="D5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>93</v>
-      </c>
-      <c r="G5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
         <v>95</v>
       </c>
-      <c r="B6" t="s">
-        <v>96</v>
-      </c>
       <c r="C6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" t="s">
         <v>95</v>
       </c>
-      <c r="D6" t="s">
-        <v>96</v>
-      </c>
       <c r="E6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" t="s">
         <v>95</v>
-      </c>
-      <c r="F6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G6" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -3259,22 +3262,22 @@
         <v>1467</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7">
         <v>3001</v>
       </c>
       <c r="D7" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E7">
-        <v>3101</v>
+        <v>5020</v>
       </c>
       <c r="F7">
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -3282,22 +3285,22 @@
         <v>1468</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="C8">
         <v>3002</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E8">
-        <v>3102</v>
+        <v>5021</v>
       </c>
       <c r="F8">
         <v>21</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -3305,22 +3308,22 @@
         <v>2467</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>196</v>
       </c>
       <c r="C9">
         <v>3003</v>
       </c>
       <c r="D9" t="s">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="E9">
-        <v>3103</v>
+        <v>5022</v>
       </c>
       <c r="F9">
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -3328,22 +3331,22 @@
         <v>2468</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C10">
         <v>3004</v>
       </c>
       <c r="D10" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="E10">
-        <v>3104</v>
+        <v>5023</v>
       </c>
       <c r="F10">
         <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -3351,22 +3354,22 @@
         <v>1457</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C11">
         <v>3005</v>
       </c>
       <c r="D11" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E11">
-        <v>3105</v>
+        <v>5024</v>
       </c>
       <c r="F11">
         <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -3374,22 +3377,22 @@
         <v>1458</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C12">
         <v>3006</v>
       </c>
       <c r="D12" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E12">
-        <v>3106</v>
+        <v>5025</v>
       </c>
       <c r="F12">
         <v>25</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -3397,22 +3400,22 @@
         <v>2457</v>
       </c>
       <c r="B13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C13">
         <v>3007</v>
       </c>
       <c r="D13" t="s">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="E13">
-        <v>3107</v>
+        <v>5026</v>
       </c>
       <c r="F13">
         <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -3420,22 +3423,22 @@
         <v>2458</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C14">
         <v>3008</v>
       </c>
       <c r="D14" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="E14">
-        <v>3108</v>
+        <v>5027</v>
       </c>
       <c r="F14">
         <v>27</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -3443,22 +3446,22 @@
         <v>1367</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C15">
         <v>3009</v>
       </c>
       <c r="D15" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E15">
-        <v>3109</v>
+        <v>5028</v>
       </c>
       <c r="F15">
         <v>28</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -3466,22 +3469,22 @@
         <v>1357</v>
       </c>
       <c r="B16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C16">
         <v>3010</v>
       </c>
       <c r="D16" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="E16">
-        <v>3110</v>
+        <v>5029</v>
       </c>
       <c r="F16">
         <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -3489,22 +3492,22 @@
         <v>2367</v>
       </c>
       <c r="B17" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C17">
         <v>3011</v>
       </c>
       <c r="D17" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E17">
-        <v>3111</v>
+        <v>5030</v>
       </c>
       <c r="F17">
         <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>72</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -3512,22 +3515,22 @@
         <v>2357</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C18">
         <v>3012</v>
       </c>
       <c r="D18" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E18">
-        <v>3112</v>
+        <v>5031</v>
       </c>
       <c r="F18">
         <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -3535,22 +3538,22 @@
         <v>1368</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C19">
         <v>3013</v>
       </c>
       <c r="D19" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E19">
-        <v>3113</v>
+        <v>5032</v>
       </c>
       <c r="F19">
         <v>32</v>
       </c>
       <c r="G19" t="s">
-        <v>77</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -3558,22 +3561,22 @@
         <v>1358</v>
       </c>
       <c r="B20" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C20">
         <v>3014</v>
       </c>
       <c r="D20" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="E20">
-        <v>3114</v>
+        <v>5033</v>
       </c>
       <c r="F20">
         <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -3581,22 +3584,22 @@
         <v>2368</v>
       </c>
       <c r="B21" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C21">
         <v>3015</v>
       </c>
       <c r="D21" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="E21">
-        <v>3115</v>
+        <v>5034</v>
       </c>
       <c r="F21">
         <v>34</v>
       </c>
       <c r="G21" t="s">
-        <v>83</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -3604,27 +3607,27 @@
         <v>2358</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C22">
         <v>3016</v>
       </c>
       <c r="D22" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E22">
-        <v>3116</v>
+        <v>5035</v>
       </c>
       <c r="F22">
         <v>35</v>
       </c>
       <c r="G22" t="s">
-        <v>83</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -3643,76 +3646,76 @@
   <sheetData>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
         <v>84</v>
       </c>
-      <c r="B3" t="s">
-        <v>85</v>
-      </c>
       <c r="C3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" t="s">
         <v>113</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>114</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>115</v>
       </c>
-      <c r="F3" t="s">
-        <v>116</v>
-      </c>
       <c r="G3" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" t="s">
         <v>90</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>91</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" t="s">
         <v>92</v>
       </c>
-      <c r="D5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>93</v>
-      </c>
-      <c r="G5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
         <v>95</v>
       </c>
-      <c r="B6" t="s">
-        <v>96</v>
-      </c>
       <c r="C6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" t="s">
         <v>95</v>
       </c>
-      <c r="D6" t="s">
-        <v>96</v>
-      </c>
       <c r="E6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" t="s">
         <v>95</v>
-      </c>
-      <c r="F6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G6" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -3720,13 +3723,13 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C7">
         <v>4001</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>213</v>
       </c>
       <c r="E7">
         <v>4101</v>
@@ -3735,7 +3738,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -3743,13 +3746,13 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C8">
         <v>4002</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>214</v>
       </c>
       <c r="E8">
         <v>4102</v>
@@ -3758,7 +3761,7 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -3766,13 +3769,13 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C9">
         <v>4003</v>
       </c>
       <c r="D9" t="s">
-        <v>140</v>
+        <v>215</v>
       </c>
       <c r="E9">
         <v>4103</v>
@@ -3781,7 +3784,7 @@
         <v>3</v>
       </c>
       <c r="G9" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -3789,13 +3792,13 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C10">
         <v>4004</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>216</v>
       </c>
       <c r="E10">
         <v>4104</v>
@@ -3804,7 +3807,7 @@
         <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -3812,13 +3815,13 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C11">
         <v>4005</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="E11">
         <v>4105</v>
@@ -3827,7 +3830,7 @@
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -3835,13 +3838,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C12">
         <v>4006</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E12">
         <v>4106</v>
@@ -3850,7 +3853,7 @@
         <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -3858,13 +3861,13 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C13">
         <v>4007</v>
       </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="E13">
         <v>4107</v>
@@ -3873,7 +3876,7 @@
         <v>7</v>
       </c>
       <c r="G13" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -3881,13 +3884,13 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C14">
         <v>4008</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="E14">
         <v>4108</v>
@@ -3896,12 +3899,12 @@
         <v>8</v>
       </c>
       <c r="G14" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
